--- a/excel_exports/石滩区分区计量.xlsx
+++ b/excel_exports/石滩区分区计量.xlsx
@@ -1166,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col width="5.28318584070797" customWidth="1" style="1" min="1" max="1"/>
@@ -3408,7 +3408,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="E88" s="0" t="inlineStr">
         <is>
@@ -3584,8 +3583,9 @@
         <v>0</v>
       </c>
     </row>
+    <row r="94"/>
     <row r="95">
-      <c r="E95" t="inlineStr">
+      <c r="E95" s="0" t="inlineStr">
         <is>
           <t>2026年4月</t>
         </is>
@@ -3756,6 +3756,181 @@
         <v>0</v>
       </c>
       <c r="J100" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026年5月</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>荔新大道</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>宁西总表（插入式）DN1200</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>如丰大道</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>新城大道医院NB</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="inlineStr">
+        <is>
+          <t>三棵竹</t>
+        </is>
+      </c>
+      <c r="G103" s="15" t="inlineStr">
+        <is>
+          <t>供水量</t>
+        </is>
+      </c>
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>售水量</t>
+        </is>
+      </c>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>损耗水量</t>
+        </is>
+      </c>
+      <c r="J103" s="13" t="inlineStr">
+        <is>
+          <t>水损耗（百分比）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>1区</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>2区</t>
+        </is>
+      </c>
+      <c r="B105" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>3区</t>
+        </is>
+      </c>
+      <c r="B106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="F107" s="15" t="inlineStr">
+        <is>
+          <t>合计:</t>
+        </is>
+      </c>
+      <c r="G107" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/excel_exports/石滩区分区计量.xlsx
+++ b/excel_exports/石滩区分区计量.xlsx
@@ -1166,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col width="5.28318584070797" customWidth="1" style="1" min="1" max="1"/>
@@ -3583,7 +3583,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="E95" s="0" t="inlineStr">
         <is>
@@ -3759,8 +3758,9 @@
         <v>0</v>
       </c>
     </row>
+    <row r="101"/>
     <row r="102">
-      <c r="E102" t="inlineStr">
+      <c r="E102" s="0" t="inlineStr">
         <is>
           <t>2026年5月</t>
         </is>
@@ -3931,6 +3931,181 @@
         <v>0</v>
       </c>
       <c r="J107" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026年6月</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>荔新大道</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>宁西总表（插入式）DN1200</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>如丰大道</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>新城大道医院NB</t>
+        </is>
+      </c>
+      <c r="F110" s="13" t="inlineStr">
+        <is>
+          <t>三棵竹</t>
+        </is>
+      </c>
+      <c r="G110" s="15" t="inlineStr">
+        <is>
+          <t>供水量</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="inlineStr">
+        <is>
+          <t>售水量</t>
+        </is>
+      </c>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>损耗水量</t>
+        </is>
+      </c>
+      <c r="J110" s="13" t="inlineStr">
+        <is>
+          <t>水损耗（百分比）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>1区</t>
+        </is>
+      </c>
+      <c r="B111" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>2区</t>
+        </is>
+      </c>
+      <c r="B112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>3区</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="F114" s="15" t="inlineStr">
+        <is>
+          <t>合计:</t>
+        </is>
+      </c>
+      <c r="G114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/excel_exports/石滩区分区计量.xlsx
+++ b/excel_exports/石滩区分区计量.xlsx
@@ -1166,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col width="5.28318584070797" customWidth="1" style="1" min="1" max="1"/>
@@ -3758,7 +3758,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="E102" s="0" t="inlineStr">
         <is>
@@ -3934,8 +3933,9 @@
         <v>0</v>
       </c>
     </row>
+    <row r="108"/>
     <row r="109">
-      <c r="E109" t="inlineStr">
+      <c r="E109" s="0" t="inlineStr">
         <is>
           <t>2026年6月</t>
         </is>
@@ -4106,6 +4106,181 @@
         <v>0</v>
       </c>
       <c r="J114" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="15" t="inlineStr">
+        <is>
+          <t>荔新大道</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>宁西总表（插入式）DN1200</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>如丰大道</t>
+        </is>
+      </c>
+      <c r="E117" s="10" t="inlineStr">
+        <is>
+          <t>新城大道医院NB</t>
+        </is>
+      </c>
+      <c r="F117" s="13" t="inlineStr">
+        <is>
+          <t>三棵竹</t>
+        </is>
+      </c>
+      <c r="G117" s="15" t="inlineStr">
+        <is>
+          <t>供水量</t>
+        </is>
+      </c>
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t>售水量</t>
+        </is>
+      </c>
+      <c r="I117" s="10" t="inlineStr">
+        <is>
+          <t>损耗水量</t>
+        </is>
+      </c>
+      <c r="J117" s="13" t="inlineStr">
+        <is>
+          <t>水损耗（百分比）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>1区</t>
+        </is>
+      </c>
+      <c r="B118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>2区</t>
+        </is>
+      </c>
+      <c r="B119" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>3区</t>
+        </is>
+      </c>
+      <c r="B120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="F121" s="15" t="inlineStr">
+        <is>
+          <t>合计:</t>
+        </is>
+      </c>
+      <c r="G121" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/excel_exports/石滩区分区计量.xlsx
+++ b/excel_exports/石滩区分区计量.xlsx
@@ -1166,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col width="5.28318584070797" customWidth="1" style="1" min="1" max="1"/>
@@ -3933,7 +3933,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108"/>
     <row r="109">
       <c r="E109" s="0" t="inlineStr">
         <is>
@@ -4109,8 +4108,9 @@
         <v>0</v>
       </c>
     </row>
+    <row r="115"/>
     <row r="116">
-      <c r="E116" t="inlineStr">
+      <c r="E116" s="0" t="inlineStr">
         <is>
           <t>2026年7月</t>
         </is>
@@ -4281,6 +4281,181 @@
         <v>0</v>
       </c>
       <c r="J121" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026年8月</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="15" t="inlineStr">
+        <is>
+          <t>荔新大道</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>宁西总表（插入式）DN1200</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>如丰大道</t>
+        </is>
+      </c>
+      <c r="E124" s="10" t="inlineStr">
+        <is>
+          <t>新城大道医院NB</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="inlineStr">
+        <is>
+          <t>三棵竹</t>
+        </is>
+      </c>
+      <c r="G124" s="15" t="inlineStr">
+        <is>
+          <t>供水量</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr">
+        <is>
+          <t>售水量</t>
+        </is>
+      </c>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>损耗水量</t>
+        </is>
+      </c>
+      <c r="J124" s="13" t="inlineStr">
+        <is>
+          <t>水损耗（百分比）</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>1区</t>
+        </is>
+      </c>
+      <c r="B125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>2区</t>
+        </is>
+      </c>
+      <c r="B126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>3区</t>
+        </is>
+      </c>
+      <c r="B127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="F128" s="15" t="inlineStr">
+        <is>
+          <t>合计:</t>
+        </is>
+      </c>
+      <c r="G128" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/excel_exports/石滩区分区计量.xlsx
+++ b/excel_exports/石滩区分区计量.xlsx
@@ -1166,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col width="5.28318584070797" customWidth="1" style="1" min="1" max="1"/>
@@ -4108,7 +4108,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115"/>
     <row r="116">
       <c r="E116" s="0" t="inlineStr">
         <is>
@@ -4284,8 +4283,9 @@
         <v>0</v>
       </c>
     </row>
+    <row r="122"/>
     <row r="123">
-      <c r="E123" t="inlineStr">
+      <c r="E123" s="0" t="inlineStr">
         <is>
           <t>2026年8月</t>
         </is>
@@ -4456,6 +4456,181 @@
         <v>0</v>
       </c>
       <c r="J128" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026年9月</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="15" t="inlineStr">
+        <is>
+          <t>荔新大道</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>宁西总表（插入式）DN1200</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>如丰大道</t>
+        </is>
+      </c>
+      <c r="E131" s="10" t="inlineStr">
+        <is>
+          <t>新城大道医院NB</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="inlineStr">
+        <is>
+          <t>三棵竹</t>
+        </is>
+      </c>
+      <c r="G131" s="15" t="inlineStr">
+        <is>
+          <t>供水量</t>
+        </is>
+      </c>
+      <c r="H131" s="10" t="inlineStr">
+        <is>
+          <t>售水量</t>
+        </is>
+      </c>
+      <c r="I131" s="10" t="inlineStr">
+        <is>
+          <t>损耗水量</t>
+        </is>
+      </c>
+      <c r="J131" s="13" t="inlineStr">
+        <is>
+          <t>水损耗（百分比）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>1区</t>
+        </is>
+      </c>
+      <c r="B132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>2区</t>
+        </is>
+      </c>
+      <c r="B133" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>3区</t>
+        </is>
+      </c>
+      <c r="B134" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="F135" s="15" t="inlineStr">
+        <is>
+          <t>合计:</t>
+        </is>
+      </c>
+      <c r="G135" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/excel_exports/石滩区分区计量.xlsx
+++ b/excel_exports/石滩区分区计量.xlsx
@@ -1166,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J142"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col width="5.28318584070797" customWidth="1" style="1" min="1" max="1"/>
@@ -4283,7 +4283,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122"/>
     <row r="123">
       <c r="E123" s="0" t="inlineStr">
         <is>
@@ -4459,8 +4458,9 @@
         <v>0</v>
       </c>
     </row>
+    <row r="129"/>
     <row r="130">
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="0" t="inlineStr">
         <is>
           <t>2026年9月</t>
         </is>
@@ -4631,6 +4631,181 @@
         <v>0</v>
       </c>
       <c r="J135" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026年10月</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="15" t="inlineStr">
+        <is>
+          <t>荔新大道</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>宁西总表（插入式）DN1200</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>如丰大道</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>新城大道医院NB</t>
+        </is>
+      </c>
+      <c r="F138" s="13" t="inlineStr">
+        <is>
+          <t>三棵竹</t>
+        </is>
+      </c>
+      <c r="G138" s="15" t="inlineStr">
+        <is>
+          <t>供水量</t>
+        </is>
+      </c>
+      <c r="H138" s="10" t="inlineStr">
+        <is>
+          <t>售水量</t>
+        </is>
+      </c>
+      <c r="I138" s="10" t="inlineStr">
+        <is>
+          <t>损耗水量</t>
+        </is>
+      </c>
+      <c r="J138" s="13" t="inlineStr">
+        <is>
+          <t>水损耗（百分比）</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>1区</t>
+        </is>
+      </c>
+      <c r="B139" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>2区</t>
+        </is>
+      </c>
+      <c r="B140" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>3区</t>
+        </is>
+      </c>
+      <c r="B141" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="F142" s="15" t="inlineStr">
+        <is>
+          <t>合计:</t>
+        </is>
+      </c>
+      <c r="G142" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="19" t="n">
         <v>0</v>
       </c>
     </row>
